--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -720,22 +716,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R2" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,24 +813,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R3" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492211</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121491566</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -716,22 +720,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R2" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +817,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R3" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -720,22 +716,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R2" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,24 +813,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R3" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492211</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>121491566</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -716,22 +720,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R2" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +817,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R3" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -720,22 +716,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R2" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,24 +813,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R3" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121492211</v>
+        <v>121491566</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>adult</t>
@@ -716,22 +720,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollberget, Trollberget, Vstm</t>
+          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547367</v>
+        <v>547493</v>
       </c>
       <c r="R2" t="n">
-        <v>6621067</v>
+        <v>6620634</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121491566</v>
+        <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,28 +817,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,22 +842,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålsbäcken, Ålsbäcken, Vstm</t>
+          <t>Trollberget, Trollberget, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547493</v>
+        <v>547367</v>
       </c>
       <c r="R3" t="n">
-        <v>6620634</v>
+        <v>6621067</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121491566</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -804,11 +804,11 @@
         <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121491566</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -819,11 +819,6 @@
       <c r="E3" t="n">
         <v>100049</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 52131-2024 artfynd.xlsx
+++ b/artfynd/A 52131-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>121492211</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,6 +818,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
